--- a/tests/e2e/tests/fixtures/import_v2_asg_items.xlsx
+++ b/tests/e2e/tests/fixtures/import_v2_asg_items.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>РотаASG [Петренко]</t>
+          <t>РотаASG Петренко</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>РотаASG [Петренко]</t>
+          <t>РотаASG Петренко</t>
         </is>
       </c>
     </row>
